--- a/inventories/baseline/lci-Salar-de-Atacama.xlsx
+++ b/inventories/baseline/lci-Salar-de-Atacama.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leidenuniv1-my.sharepoint.com/personal/istrateir_vuw_leidenuniv_nl/Documents/Research/lithium-brine-prospective-LCA/inventories/raw/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_70719CCDF3E7F8CCF47548FA6595D3557394200B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0739902B-F8B1-457E-B0E9-74ABFA6E9EE3}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Salar de Atacama" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -235,8 +229,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -282,21 +276,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -334,7 +320,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -368,7 +354,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -403,10 +388,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -579,15 +563,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F282"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="63.85546875" customWidth="1"/>
-    <col min="2" max="2" width="106" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,7 +575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -603,7 +583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -611,7 +591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -619,7 +599,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -627,7 +607,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -635,7 +615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -643,7 +623,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -651,12 +631,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -676,12 +656,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>2.5000000000000001E-4</v>
+        <v>0.00025</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -693,12 +673,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
-        <v>1.25E-3</v>
+        <v>0.00125</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -710,7 +690,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -727,12 +707,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <v>7.2059999999999997E-3</v>
+        <v>0.007206</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -744,7 +724,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -752,7 +732,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -760,7 +740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -768,7 +748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -776,7 +756,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -784,7 +764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -792,7 +772,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -800,12 +780,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -825,12 +805,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26">
-        <v>-2.0849534464459272E-3</v>
+        <v>-0.002084953446445927</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -842,7 +822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -859,12 +839,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>3</v>
       </c>
       <c r="B28">
-        <v>-4.5949995563406967E-2</v>
+        <v>-0.04594999556340697</v>
       </c>
       <c r="C28" t="s">
         <v>1</v>
@@ -876,7 +856,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -893,12 +873,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>30</v>
       </c>
       <c r="B30">
-        <v>2.7629090730522599E-2</v>
+        <v>0.0276290907305226</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
@@ -910,12 +890,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31">
-        <v>2.4744089248118491E-2</v>
+        <v>0.02474408924811849</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -927,12 +907,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32">
-        <v>1.4919354838709681E-2</v>
+        <v>0.01491935483870968</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -944,12 +924,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33">
-        <v>3.7116133872177768E-4</v>
+        <v>0.0003711613387217777</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -961,12 +941,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34">
-        <v>-3.7527416370743943E-2</v>
+        <v>-0.03752741637074394</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
@@ -978,7 +958,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" s="1" t="s">
         <v>2</v>
       </c>
@@ -986,7 +966,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -994,7 +974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1002,7 +982,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -1010,7 +990,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -1018,7 +998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1026,7 +1006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -1034,12 +1014,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1059,12 +1039,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>27</v>
       </c>
       <c r="B45">
-        <v>-0.13009701902699849</v>
+        <v>-0.1300970190269985</v>
       </c>
       <c r="D45" t="s">
         <v>28</v>
@@ -1076,7 +1056,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -1093,12 +1073,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>38</v>
       </c>
       <c r="B47">
-        <v>1.9638491504655591</v>
+        <v>1.963849150465559</v>
       </c>
       <c r="C47" t="s">
         <v>1</v>
@@ -1110,7 +1090,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -1127,7 +1107,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" s="1" t="s">
         <v>2</v>
       </c>
@@ -1135,7 +1115,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1143,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1151,7 +1131,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -1159,7 +1139,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -1167,7 +1147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -1175,7 +1155,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -1183,12 +1163,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -1208,7 +1188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -1225,12 +1205,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>3</v>
       </c>
       <c r="B60">
-        <v>0.32481935841419379</v>
+        <v>0.3248193584141938</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1242,12 +1222,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>41</v>
       </c>
       <c r="B61">
-        <v>0.59397580198225786</v>
+        <v>0.5939758019822579</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -1259,12 +1239,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>39</v>
       </c>
       <c r="B62">
-        <v>0.16570100588261369</v>
+        <v>0.1657010058826137</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -1276,12 +1256,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>42</v>
       </c>
       <c r="B63">
-        <v>8.1204839603548462E-2</v>
+        <v>0.08120483960354846</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
@@ -1293,7 +1273,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6">
       <c r="A65" s="1" t="s">
         <v>2</v>
       </c>
@@ -1301,7 +1281,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -1309,7 +1289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -1317,7 +1297,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -1325,7 +1305,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -1333,7 +1313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -1341,7 +1321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -1349,12 +1329,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -1374,7 +1354,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>43</v>
       </c>
@@ -1391,12 +1371,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>3</v>
       </c>
       <c r="B75">
-        <v>5.8605080052129136E-4</v>
+        <v>0.0005860508005212914</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1408,12 +1388,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>44</v>
       </c>
       <c r="B76">
-        <v>0.99758962819795594</v>
+        <v>0.9975896281979559</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1425,12 +1405,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>45</v>
       </c>
       <c r="B77">
-        <v>1.8243210015228141E-3</v>
+        <v>0.001824321001522814</v>
       </c>
       <c r="C77" t="s">
         <v>31</v>
@@ -1442,7 +1422,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" s="1" t="s">
         <v>2</v>
       </c>
@@ -1450,7 +1430,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -1458,7 +1438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -1466,7 +1446,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -1474,7 +1454,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>7</v>
       </c>
@@ -1482,7 +1462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -1490,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -1498,12 +1478,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -1523,12 +1503,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>27</v>
       </c>
       <c r="B88">
-        <v>-5.0112919960215808E-2</v>
+        <v>-0.05011291996021581</v>
       </c>
       <c r="D88" t="s">
         <v>28</v>
@@ -1540,7 +1520,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>46</v>
       </c>
@@ -1557,12 +1537,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>3</v>
       </c>
       <c r="B90">
-        <v>5.2961186205221882E-2</v>
+        <v>0.05296118620522188</v>
       </c>
       <c r="C90" t="s">
         <v>1</v>
@@ -1574,12 +1554,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>47</v>
       </c>
       <c r="B91">
-        <v>0.15563308620724539</v>
+        <v>0.1556330862072454</v>
       </c>
       <c r="C91" t="s">
         <v>1</v>
@@ -1591,12 +1571,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>42</v>
       </c>
       <c r="B92">
-        <v>1.324029655130547E-2</v>
+        <v>0.01324029655130547</v>
       </c>
       <c r="C92" t="s">
         <v>33</v>
@@ -1608,7 +1588,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" s="1" t="s">
         <v>2</v>
       </c>
@@ -1616,7 +1596,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -1624,7 +1604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -1632,7 +1612,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -1640,7 +1620,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -1648,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -1656,7 +1636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -1664,12 +1644,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>13</v>
       </c>
@@ -1689,7 +1669,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>48</v>
       </c>
@@ -1706,12 +1686,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>37</v>
       </c>
       <c r="B104">
-        <v>7.7164002898357626</v>
+        <v>7.716400289835763</v>
       </c>
       <c r="C104" t="s">
         <v>1</v>
@@ -1723,12 +1703,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>22</v>
       </c>
       <c r="B105">
-        <v>8.2022243473315552E-3</v>
+        <v>0.008202224347331555</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
@@ -1740,12 +1720,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>49</v>
       </c>
       <c r="B106">
-        <v>-6.716400289835763E-3</v>
+        <v>-0.006716400289835763</v>
       </c>
       <c r="C106" t="s">
         <v>1</v>
@@ -1757,7 +1737,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" s="1" t="s">
         <v>2</v>
       </c>
@@ -1765,7 +1745,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -1773,7 +1753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -1781,7 +1761,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -1789,7 +1769,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>7</v>
       </c>
@@ -1797,7 +1777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -1805,7 +1785,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -1813,12 +1793,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>13</v>
       </c>
@@ -1838,7 +1818,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>50</v>
       </c>
@@ -1855,7 +1835,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -1872,12 +1852,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>22</v>
       </c>
       <c r="B119">
-        <v>1.6273083822264979E-2</v>
+        <v>0.01627308382226498</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -1889,12 +1869,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>49</v>
       </c>
       <c r="B120">
-        <v>-7.0804010907046418E-3</v>
+        <v>-0.007080401090704642</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -1906,7 +1886,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6">
       <c r="A122" s="1" t="s">
         <v>2</v>
       </c>
@@ -1914,7 +1894,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -1922,7 +1902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -1930,7 +1910,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -1938,7 +1918,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>7</v>
       </c>
@@ -1946,7 +1926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>8</v>
       </c>
@@ -1954,7 +1934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -1962,12 +1942,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6">
       <c r="A129" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -1987,7 +1967,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>47</v>
       </c>
@@ -2004,12 +1984,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>26</v>
       </c>
       <c r="B132">
-        <v>1.0526315789473679</v>
+        <v>1.052631578947368</v>
       </c>
       <c r="C132" t="s">
         <v>1</v>
@@ -2021,12 +2001,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>22</v>
       </c>
       <c r="B133">
-        <v>5.263157894736842E-4</v>
+        <v>0.0005263157894736842</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -2038,12 +2018,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>36</v>
       </c>
       <c r="B134">
-        <v>-5.2631578947368418E-2</v>
+        <v>-0.05263157894736842</v>
       </c>
       <c r="C134" t="s">
         <v>31</v>
@@ -2055,7 +2035,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6">
       <c r="A136" s="1" t="s">
         <v>2</v>
       </c>
@@ -2063,7 +2043,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -2071,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -2079,7 +2059,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -2087,7 +2067,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -2095,7 +2075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -2103,7 +2083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -2111,12 +2091,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6">
       <c r="A143" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -2136,7 +2116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>41</v>
       </c>
@@ -2153,12 +2133,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>43</v>
       </c>
       <c r="B146">
-        <v>1.0042519558214309</v>
+        <v>1.004251955821431</v>
       </c>
       <c r="C146" t="s">
         <v>1</v>
@@ -2170,12 +2150,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>22</v>
       </c>
       <c r="B147">
-        <v>4.25195582143068E-5</v>
+        <v>4.25195582143068E-05</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -2187,12 +2167,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>36</v>
       </c>
       <c r="B148">
-        <v>-4.2519558214306804E-3</v>
+        <v>-0.00425195582143068</v>
       </c>
       <c r="C148" t="s">
         <v>31</v>
@@ -2204,7 +2184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6">
       <c r="A150" s="1" t="s">
         <v>2</v>
       </c>
@@ -2212,7 +2192,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -2220,7 +2200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -2228,7 +2208,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>6</v>
       </c>
@@ -2236,7 +2216,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>7</v>
       </c>
@@ -2244,7 +2224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>8</v>
       </c>
@@ -2252,7 +2232,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>10</v>
       </c>
@@ -2260,12 +2240,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6">
       <c r="A157" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>13</v>
       </c>
@@ -2285,7 +2265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>44</v>
       </c>
@@ -2302,7 +2282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>46</v>
       </c>
@@ -2319,12 +2299,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>22</v>
       </c>
       <c r="B161">
-        <v>1.9715155015009251E-4</v>
+        <v>0.0001971515501500925</v>
       </c>
       <c r="C161" t="s">
         <v>23</v>
@@ -2336,12 +2316,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>36</v>
       </c>
       <c r="B162">
-        <v>-1.9715155015009249E-2</v>
+        <v>-0.01971515501500925</v>
       </c>
       <c r="C162" t="s">
         <v>31</v>
@@ -2353,7 +2333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6">
       <c r="A164" s="1" t="s">
         <v>2</v>
       </c>
@@ -2361,7 +2341,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>4</v>
       </c>
@@ -2369,7 +2349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>5</v>
       </c>
@@ -2377,7 +2357,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -2385,7 +2365,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -2393,7 +2373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>8</v>
       </c>
@@ -2401,7 +2381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -2409,12 +2389,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6">
       <c r="A171" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>13</v>
       </c>
@@ -2434,7 +2414,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>51</v>
       </c>
@@ -2451,7 +2431,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>52</v>
       </c>
@@ -2468,12 +2448,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>22</v>
       </c>
       <c r="B175">
-        <v>2.4802398473698548E-3</v>
+        <v>0.002480239847369855</v>
       </c>
       <c r="C175" t="s">
         <v>23</v>
@@ -2485,12 +2465,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>49</v>
       </c>
       <c r="B176">
-        <v>-1.3333333333333331E-3</v>
+        <v>-0.001333333333333333</v>
       </c>
       <c r="C176" t="s">
         <v>1</v>
@@ -2502,7 +2482,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6">
       <c r="A178" s="1" t="s">
         <v>2</v>
       </c>
@@ -2510,7 +2490,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>4</v>
       </c>
@@ -2518,7 +2498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>5</v>
       </c>
@@ -2526,7 +2506,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>6</v>
       </c>
@@ -2534,7 +2514,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>7</v>
       </c>
@@ -2542,7 +2522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -2550,7 +2530,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -2558,12 +2538,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6">
       <c r="A185" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>13</v>
       </c>
@@ -2583,7 +2563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>38</v>
       </c>
@@ -2600,12 +2580,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>3</v>
       </c>
       <c r="B188">
-        <v>0.84602368866328248</v>
+        <v>0.8460236886632825</v>
       </c>
       <c r="C188" t="s">
         <v>1</v>
@@ -2617,12 +2597,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>53</v>
       </c>
       <c r="B189">
-        <v>0.15397631133671741</v>
+        <v>0.1539763113367174</v>
       </c>
       <c r="C189" t="s">
         <v>1</v>
@@ -2634,7 +2614,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>22</v>
       </c>
@@ -2651,7 +2631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6">
       <c r="A192" s="1" t="s">
         <v>2</v>
       </c>
@@ -2659,7 +2639,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -2667,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -2675,7 +2655,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -2683,7 +2663,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>7</v>
       </c>
@@ -2691,7 +2671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>8</v>
       </c>
@@ -2699,7 +2679,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -2707,12 +2687,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6">
       <c r="A199" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -2732,7 +2712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>55</v>
       </c>
@@ -2749,12 +2729,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>56</v>
       </c>
       <c r="B202">
-        <v>1.6885251263438109E-10</v>
+        <v>1.688525126343811E-10</v>
       </c>
       <c r="D202" t="s">
         <v>57</v>
@@ -2766,12 +2746,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>59</v>
       </c>
       <c r="B203">
-        <v>4.2213128158595277E-12</v>
+        <v>4.221312815859528E-12</v>
       </c>
       <c r="D203" t="s">
         <v>60</v>
@@ -2783,12 +2763,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>61</v>
       </c>
       <c r="B204">
-        <v>4.2213128158595277E-12</v>
+        <v>4.221312815859528E-12</v>
       </c>
       <c r="D204" t="s">
         <v>60</v>
@@ -2800,7 +2780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>15</v>
       </c>
@@ -2817,7 +2797,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>54</v>
       </c>
@@ -2834,12 +2814,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>3</v>
       </c>
       <c r="B207">
-        <v>6.6759001229272483</v>
+        <v>6.675900122927248</v>
       </c>
       <c r="C207" t="s">
         <v>1</v>
@@ -2851,12 +2831,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>62</v>
       </c>
       <c r="B208">
-        <v>2.6136816379141169E-4</v>
+        <v>0.0002613681637914117</v>
       </c>
       <c r="C208" t="s">
         <v>1</v>
@@ -2868,12 +2848,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>22</v>
       </c>
       <c r="B209">
-        <v>1.9086291285683881E-2</v>
+        <v>0.01908629128568388</v>
       </c>
       <c r="C209" t="s">
         <v>23</v>
@@ -2885,7 +2865,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>45</v>
       </c>
@@ -2902,12 +2882,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>64</v>
       </c>
       <c r="B211">
-        <v>1.201662022126905E-2</v>
+        <v>0.01201662022126905</v>
       </c>
       <c r="C211" t="s">
         <v>31</v>
@@ -2919,12 +2899,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>65</v>
       </c>
       <c r="B212">
-        <v>-31.982474761904331</v>
+        <v>-31.98247476190433</v>
       </c>
       <c r="C212" t="s">
         <v>31</v>
@@ -2936,12 +2916,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>49</v>
       </c>
       <c r="B213">
-        <v>-6.6759001229272476E-3</v>
+        <v>-0.006675900122927248</v>
       </c>
       <c r="C213" t="s">
         <v>1</v>
@@ -2953,7 +2933,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6">
       <c r="A215" s="1" t="s">
         <v>2</v>
       </c>
@@ -2961,7 +2941,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>4</v>
       </c>
@@ -2969,7 +2949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>5</v>
       </c>
@@ -2977,7 +2957,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -2985,7 +2965,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>7</v>
       </c>
@@ -2993,7 +2973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>8</v>
       </c>
@@ -3001,7 +2981,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>10</v>
       </c>
@@ -3009,12 +2989,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6">
       <c r="A222" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -3034,7 +3014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6">
       <c r="A224" t="s">
         <v>27</v>
       </c>
@@ -3051,7 +3031,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6">
       <c r="A225" t="s">
         <v>66</v>
       </c>
@@ -3068,7 +3048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>51</v>
       </c>
@@ -3085,12 +3065,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6">
       <c r="A227" t="s">
         <v>39</v>
       </c>
       <c r="B227">
-        <v>0.35294117647058831</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="C227" t="s">
         <v>1</v>
@@ -3102,7 +3082,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>22</v>
       </c>
@@ -3119,7 +3099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6">
       <c r="A230" s="1" t="s">
         <v>2</v>
       </c>
@@ -3127,7 +3107,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>4</v>
       </c>
@@ -3135,7 +3115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6">
       <c r="A232" t="s">
         <v>5</v>
       </c>
@@ -3143,7 +3123,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -3151,7 +3131,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6">
       <c r="A234" t="s">
         <v>7</v>
       </c>
@@ -3159,7 +3139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>8</v>
       </c>
@@ -3167,7 +3147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -3175,12 +3155,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6">
       <c r="A237" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>13</v>
       </c>
@@ -3200,7 +3180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>29</v>
       </c>
@@ -3217,7 +3197,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>54</v>
       </c>
@@ -3234,7 +3214,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6">
       <c r="A241" t="s">
         <v>67</v>
       </c>
@@ -3251,7 +3231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6">
       <c r="A243" s="1" t="s">
         <v>2</v>
       </c>
@@ -3259,7 +3239,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6">
       <c r="A244" t="s">
         <v>4</v>
       </c>
@@ -3267,7 +3247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>5</v>
       </c>
@@ -3275,7 +3255,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -3283,7 +3263,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6">
       <c r="A247" t="s">
         <v>7</v>
       </c>
@@ -3291,7 +3271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6">
       <c r="A248" t="s">
         <v>8</v>
       </c>
@@ -3299,7 +3279,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -3307,12 +3287,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6">
       <c r="A250" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6">
       <c r="A251" t="s">
         <v>13</v>
       </c>
@@ -3332,7 +3312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6">
       <c r="A252" t="s">
         <v>52</v>
       </c>
@@ -3349,7 +3329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>3</v>
       </c>
@@ -3366,12 +3346,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>48</v>
       </c>
       <c r="B254">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C254" t="s">
         <v>1</v>
@@ -3383,12 +3363,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6">
       <c r="A255" t="s">
         <v>39</v>
       </c>
       <c r="B255">
-        <v>0.25391352967975522</v>
+        <v>0.2539135296797552</v>
       </c>
       <c r="C255" t="s">
         <v>1</v>
@@ -3400,7 +3380,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="257" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6">
       <c r="A257" s="1" t="s">
         <v>2</v>
       </c>
@@ -3408,7 +3388,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>4</v>
       </c>
@@ -3416,7 +3396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>5</v>
       </c>
@@ -3424,7 +3404,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>6</v>
       </c>
@@ -3432,7 +3412,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>7</v>
       </c>
@@ -3440,7 +3420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>8</v>
       </c>
@@ -3448,7 +3428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>10</v>
       </c>
@@ -3456,12 +3436,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="264" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6">
       <c r="A264" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>13</v>
       </c>
@@ -3481,7 +3461,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>53</v>
       </c>
@@ -3498,7 +3478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>3</v>
       </c>
@@ -3515,12 +3495,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>50</v>
       </c>
       <c r="B268">
-        <v>0.42857142857142849</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="C268" t="s">
         <v>1</v>
@@ -3532,12 +3512,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>39</v>
       </c>
       <c r="B269">
-        <v>0.25391352967975522</v>
+        <v>0.2539135296797552</v>
       </c>
       <c r="C269" t="s">
         <v>1</v>
@@ -3549,7 +3529,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6">
       <c r="A271" s="1" t="s">
         <v>2</v>
       </c>
@@ -3557,7 +3537,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>4</v>
       </c>
@@ -3565,7 +3545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -3573,7 +3553,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -3581,7 +3561,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>7</v>
       </c>
@@ -3589,7 +3569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>8</v>
       </c>
@@ -3597,7 +3577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>10</v>
       </c>
@@ -3605,12 +3585,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="278" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6">
       <c r="A278" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>13</v>
       </c>
@@ -3630,7 +3610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>15</v>
       </c>
@@ -3647,7 +3627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>49</v>
       </c>
@@ -3664,7 +3644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>69</v>
       </c>

--- a/inventories/baseline/lci-Salar-de-Atacama.xlsx
+++ b/inventories/baseline/lci-Salar-de-Atacama.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://leidenuniv1-my.sharepoint.com/personal/istrateir_vuw_leidenuniv_nl/Documents/Research/lithium-brine-prospective-LCA/inventories/baseline/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_5D5E1A5AC6696C2F752A371DD5756C6D45787A65" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFFA51FE-AD4F-4999-BA24-8A4B0582AA32}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Salar de Atacama" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -229,8 +235,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,13 +282,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -320,7 +334,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -354,6 +368,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -388,9 +403,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -563,11 +579,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F282"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="83.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -575,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -583,7 +602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -591,7 +610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -599,7 +618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -607,7 +626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -615,7 +634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -623,7 +642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -631,12 +650,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -656,12 +675,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.00025</v>
+        <v>2.5000000000000001E-4</v>
       </c>
       <c r="D12" t="s">
         <v>16</v>
@@ -673,12 +692,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
       <c r="B13">
-        <v>0.00125</v>
+        <v>1.25E-3</v>
       </c>
       <c r="D13" t="s">
         <v>16</v>
@@ -690,7 +709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -707,12 +726,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <v>0.007206</v>
+        <v>7.2059999999999997E-3</v>
       </c>
       <c r="C15" t="s">
         <v>23</v>
@@ -724,7 +743,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>2</v>
       </c>
@@ -732,7 +751,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -740,7 +759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -748,7 +767,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -756,7 +775,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -764,7 +783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -772,7 +791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -780,12 +799,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -805,12 +824,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26">
-        <v>-0.002084953446445927</v>
+        <v>-2.0849534464459272E-3</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -822,7 +841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -839,12 +858,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
       <c r="B28">
-        <v>-0.04594999556340697</v>
+        <v>-4.5949995563406967E-2</v>
       </c>
       <c r="C28" t="s">
         <v>1</v>
@@ -856,7 +875,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -873,12 +892,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0276290907305226</v>
+        <v>2.7629090730522599E-2</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
@@ -890,12 +909,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31">
-        <v>0.02474408924811849</v>
+        <v>2.4744089248118491E-2</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -907,12 +926,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
       <c r="B32">
-        <v>0.01491935483870968</v>
+        <v>1.4919354838709681E-2</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -924,12 +943,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
       <c r="B33">
-        <v>0.0003711613387217777</v>
+        <v>3.7116133872177768E-4</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -941,12 +960,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
       <c r="B34">
-        <v>-0.03752741637074394</v>
+        <v>-3.7527416370743943E-2</v>
       </c>
       <c r="C34" t="s">
         <v>31</v>
@@ -958,7 +977,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>2</v>
       </c>
@@ -966,7 +985,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -974,7 +993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -982,7 +1001,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -990,7 +1009,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -998,7 +1017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1006,7 +1025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>10</v>
       </c>
@@ -1014,12 +1033,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -1039,12 +1058,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>27</v>
       </c>
       <c r="B45">
-        <v>-0.1300970190269985</v>
+        <v>-0.13009701902699849</v>
       </c>
       <c r="D45" t="s">
         <v>28</v>
@@ -1056,7 +1075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>37</v>
       </c>
@@ -1073,12 +1092,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>38</v>
       </c>
       <c r="B47">
-        <v>1.963849150465559</v>
+        <v>1.9638491504655591</v>
       </c>
       <c r="C47" t="s">
         <v>1</v>
@@ -1090,7 +1109,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -1107,7 +1126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>2</v>
       </c>
@@ -1115,7 +1134,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1123,7 +1142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -1131,7 +1150,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -1139,7 +1158,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>7</v>
       </c>
@@ -1147,7 +1166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -1155,7 +1174,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>10</v>
       </c>
@@ -1163,12 +1182,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -1188,7 +1207,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -1205,12 +1224,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>3</v>
       </c>
       <c r="B60">
-        <v>0.3248193584141938</v>
+        <v>0.32481935841419379</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1222,12 +1241,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>41</v>
       </c>
       <c r="B61">
-        <v>0.5939758019822579</v>
+        <v>0.59397580198225786</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -1239,12 +1258,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>39</v>
       </c>
       <c r="B62">
-        <v>0.1657010058826137</v>
+        <v>0.16570100588261369</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -1256,12 +1275,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>42</v>
       </c>
       <c r="B63">
-        <v>0.08120483960354846</v>
+        <v>8.1204839603548462E-2</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
@@ -1273,7 +1292,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>2</v>
       </c>
@@ -1281,7 +1300,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -1289,7 +1308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>5</v>
       </c>
@@ -1297,7 +1316,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -1305,7 +1324,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>7</v>
       </c>
@@ -1313,7 +1332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -1321,7 +1340,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>10</v>
       </c>
@@ -1329,12 +1348,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -1354,7 +1373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>43</v>
       </c>
@@ -1371,12 +1390,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>3</v>
       </c>
       <c r="B75">
-        <v>0.0005860508005212914</v>
+        <v>5.8605080052129136E-4</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1388,12 +1407,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>44</v>
       </c>
       <c r="B76">
-        <v>0.9975896281979559</v>
+        <v>0.99758962819795594</v>
       </c>
       <c r="C76" t="s">
         <v>1</v>
@@ -1405,12 +1424,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>45</v>
       </c>
       <c r="B77">
-        <v>0.001824321001522814</v>
+        <v>1.8243210015228141E-3</v>
       </c>
       <c r="C77" t="s">
         <v>31</v>
@@ -1422,7 +1441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>2</v>
       </c>
@@ -1430,7 +1449,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -1438,7 +1457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>5</v>
       </c>
@@ -1446,7 +1465,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -1454,7 +1473,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>7</v>
       </c>
@@ -1462,7 +1481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>8</v>
       </c>
@@ -1470,7 +1489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>10</v>
       </c>
@@ -1478,12 +1497,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -1503,12 +1522,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>27</v>
       </c>
       <c r="B88">
-        <v>-0.05011291996021581</v>
+        <v>-5.0112919960215808E-2</v>
       </c>
       <c r="D88" t="s">
         <v>28</v>
@@ -1520,7 +1539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>46</v>
       </c>
@@ -1537,12 +1556,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>3</v>
       </c>
       <c r="B90">
-        <v>0.05296118620522188</v>
+        <v>5.2961186205221882E-2</v>
       </c>
       <c r="C90" t="s">
         <v>1</v>
@@ -1554,12 +1573,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>47</v>
       </c>
       <c r="B91">
-        <v>0.1556330862072454</v>
+        <v>0.15563308620724539</v>
       </c>
       <c r="C91" t="s">
         <v>1</v>
@@ -1571,12 +1590,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>42</v>
       </c>
       <c r="B92">
-        <v>0.01324029655130547</v>
+        <v>1.324029655130547E-2</v>
       </c>
       <c r="C92" t="s">
         <v>33</v>
@@ -1588,7 +1607,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1615,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -1604,7 +1623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>5</v>
       </c>
@@ -1612,7 +1631,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>6</v>
       </c>
@@ -1620,7 +1639,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -1628,7 +1647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>8</v>
       </c>
@@ -1636,7 +1655,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>10</v>
       </c>
@@ -1644,12 +1663,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>13</v>
       </c>
@@ -1669,7 +1688,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>48</v>
       </c>
@@ -1686,12 +1705,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>37</v>
       </c>
       <c r="B104">
-        <v>7.716400289835763</v>
+        <v>7.7164002898357626</v>
       </c>
       <c r="C104" t="s">
         <v>1</v>
@@ -1703,12 +1722,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>22</v>
       </c>
       <c r="B105">
-        <v>0.008202224347331555</v>
+        <v>8.2022243473315552E-3</v>
       </c>
       <c r="C105" t="s">
         <v>23</v>
@@ -1720,12 +1739,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>49</v>
       </c>
       <c r="B106">
-        <v>-0.006716400289835763</v>
+        <v>-6.716400289835763E-3</v>
       </c>
       <c r="C106" t="s">
         <v>1</v>
@@ -1737,7 +1756,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>2</v>
       </c>
@@ -1745,7 +1764,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -1753,7 +1772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>5</v>
       </c>
@@ -1761,7 +1780,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>6</v>
       </c>
@@ -1769,7 +1788,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>7</v>
       </c>
@@ -1777,7 +1796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>8</v>
       </c>
@@ -1785,7 +1804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>10</v>
       </c>
@@ -1793,12 +1812,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>13</v>
       </c>
@@ -1818,7 +1837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>50</v>
       </c>
@@ -1835,7 +1854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -1852,12 +1871,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>22</v>
       </c>
       <c r="B119">
-        <v>0.01627308382226498</v>
+        <v>1.6273083822264979E-2</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -1869,12 +1888,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>49</v>
       </c>
       <c r="B120">
-        <v>-0.007080401090704642</v>
+        <v>-7.0804010907046418E-3</v>
       </c>
       <c r="C120" t="s">
         <v>1</v>
@@ -1886,7 +1905,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>2</v>
       </c>
@@ -1894,7 +1913,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -1902,7 +1921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -1910,7 +1929,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>6</v>
       </c>
@@ -1918,7 +1937,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>7</v>
       </c>
@@ -1926,7 +1945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>8</v>
       </c>
@@ -1934,7 +1953,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>10</v>
       </c>
@@ -1942,12 +1961,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -1967,7 +1986,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>47</v>
       </c>
@@ -1984,12 +2003,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>26</v>
       </c>
       <c r="B132">
-        <v>1.052631578947368</v>
+        <v>1.0526315789473679</v>
       </c>
       <c r="C132" t="s">
         <v>1</v>
@@ -2001,12 +2020,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>22</v>
       </c>
       <c r="B133">
-        <v>0.0005263157894736842</v>
+        <v>5.263157894736842E-4</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -2018,12 +2037,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>36</v>
       </c>
       <c r="B134">
-        <v>-0.05263157894736842</v>
+        <v>-5.2631578947368418E-2</v>
       </c>
       <c r="C134" t="s">
         <v>31</v>
@@ -2035,7 +2054,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>2</v>
       </c>
@@ -2043,7 +2062,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -2051,7 +2070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>5</v>
       </c>
@@ -2059,7 +2078,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>6</v>
       </c>
@@ -2067,7 +2086,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>7</v>
       </c>
@@ -2075,7 +2094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -2083,7 +2102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>10</v>
       </c>
@@ -2091,12 +2110,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -2116,7 +2135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>41</v>
       </c>
@@ -2133,12 +2152,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>43</v>
       </c>
       <c r="B146">
-        <v>1.004251955821431</v>
+        <v>1.0042519558214309</v>
       </c>
       <c r="C146" t="s">
         <v>1</v>
@@ -2150,12 +2169,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>22</v>
       </c>
       <c r="B147">
-        <v>4.25195582143068E-05</v>
+        <v>4.25195582143068E-5</v>
       </c>
       <c r="C147" t="s">
         <v>23</v>
@@ -2167,12 +2186,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>36</v>
       </c>
       <c r="B148">
-        <v>-0.00425195582143068</v>
+        <v>-4.2519558214306804E-3</v>
       </c>
       <c r="C148" t="s">
         <v>31</v>
@@ -2184,7 +2203,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>2</v>
       </c>
@@ -2192,7 +2211,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -2200,7 +2219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>5</v>
       </c>
@@ -2208,7 +2227,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>6</v>
       </c>
@@ -2216,7 +2235,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>7</v>
       </c>
@@ -2224,7 +2243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>8</v>
       </c>
@@ -2232,7 +2251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>10</v>
       </c>
@@ -2240,12 +2259,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>13</v>
       </c>
@@ -2265,7 +2284,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>44</v>
       </c>
@@ -2282,7 +2301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>46</v>
       </c>
@@ -2299,12 +2318,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>22</v>
       </c>
       <c r="B161">
-        <v>0.0001971515501500925</v>
+        <v>1.9715155015009251E-4</v>
       </c>
       <c r="C161" t="s">
         <v>23</v>
@@ -2316,12 +2335,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>36</v>
       </c>
       <c r="B162">
-        <v>-0.01971515501500925</v>
+        <v>-1.9715155015009249E-2</v>
       </c>
       <c r="C162" t="s">
         <v>31</v>
@@ -2333,7 +2352,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>2</v>
       </c>
@@ -2341,7 +2360,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>4</v>
       </c>
@@ -2349,7 +2368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>5</v>
       </c>
@@ -2357,7 +2376,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>6</v>
       </c>
@@ -2365,7 +2384,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>7</v>
       </c>
@@ -2373,7 +2392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>8</v>
       </c>
@@ -2381,7 +2400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>10</v>
       </c>
@@ -2389,12 +2408,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>13</v>
       </c>
@@ -2414,7 +2433,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>51</v>
       </c>
@@ -2431,7 +2450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>52</v>
       </c>
@@ -2448,12 +2467,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>22</v>
       </c>
       <c r="B175">
-        <v>0.002480239847369855</v>
+        <v>2.4802398473698548E-3</v>
       </c>
       <c r="C175" t="s">
         <v>23</v>
@@ -2465,12 +2484,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>49</v>
       </c>
       <c r="B176">
-        <v>-0.001333333333333333</v>
+        <v>-1.3333333333333331E-3</v>
       </c>
       <c r="C176" t="s">
         <v>1</v>
@@ -2482,7 +2501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>2</v>
       </c>
@@ -2490,7 +2509,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>4</v>
       </c>
@@ -2498,7 +2517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>5</v>
       </c>
@@ -2506,7 +2525,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>6</v>
       </c>
@@ -2514,7 +2533,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>7</v>
       </c>
@@ -2522,7 +2541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>8</v>
       </c>
@@ -2530,7 +2549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>10</v>
       </c>
@@ -2538,12 +2557,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>13</v>
       </c>
@@ -2563,7 +2582,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>38</v>
       </c>
@@ -2580,12 +2599,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>3</v>
       </c>
       <c r="B188">
-        <v>0.8460236886632825</v>
+        <v>0.84602368866328248</v>
       </c>
       <c r="C188" t="s">
         <v>1</v>
@@ -2597,12 +2616,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>53</v>
       </c>
       <c r="B189">
-        <v>0.1539763113367174</v>
+        <v>0.15397631133671741</v>
       </c>
       <c r="C189" t="s">
         <v>1</v>
@@ -2614,7 +2633,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>22</v>
       </c>
@@ -2631,7 +2650,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>2</v>
       </c>
@@ -2639,7 +2658,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>4</v>
       </c>
@@ -2647,7 +2666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>5</v>
       </c>
@@ -2655,7 +2674,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>6</v>
       </c>
@@ -2663,7 +2682,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>7</v>
       </c>
@@ -2671,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>8</v>
       </c>
@@ -2679,7 +2698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>10</v>
       </c>
@@ -2687,12 +2706,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -2712,7 +2731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>55</v>
       </c>
@@ -2729,12 +2748,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>56</v>
       </c>
       <c r="B202">
-        <v>1.688525126343811E-10</v>
+        <v>1.6885251263438109E-10</v>
       </c>
       <c r="D202" t="s">
         <v>57</v>
@@ -2746,12 +2765,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>59</v>
       </c>
       <c r="B203">
-        <v>4.221312815859528E-12</v>
+        <v>4.2213128158595277E-12</v>
       </c>
       <c r="D203" t="s">
         <v>60</v>
@@ -2763,12 +2782,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>61</v>
       </c>
       <c r="B204">
-        <v>4.221312815859528E-12</v>
+        <v>4.2213128158595277E-12</v>
       </c>
       <c r="D204" t="s">
         <v>60</v>
@@ -2780,7 +2799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>15</v>
       </c>
@@ -2797,7 +2816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>54</v>
       </c>
@@ -2814,12 +2833,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>3</v>
       </c>
       <c r="B207">
-        <v>6.675900122927248</v>
+        <v>6.6759001229272483</v>
       </c>
       <c r="C207" t="s">
         <v>1</v>
@@ -2831,12 +2850,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>62</v>
       </c>
       <c r="B208">
-        <v>0.0002613681637914117</v>
+        <v>2.6136816379141169E-4</v>
       </c>
       <c r="C208" t="s">
         <v>1</v>
@@ -2848,12 +2867,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>22</v>
       </c>
       <c r="B209">
-        <v>0.01908629128568388</v>
+        <v>1.9086291285683881E-2</v>
       </c>
       <c r="C209" t="s">
         <v>23</v>
@@ -2865,7 +2884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>45</v>
       </c>
@@ -2882,12 +2901,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>64</v>
       </c>
       <c r="B211">
-        <v>0.01201662022126905</v>
+        <v>1.201662022126905E-2</v>
       </c>
       <c r="C211" t="s">
         <v>31</v>
@@ -2899,12 +2918,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>65</v>
       </c>
       <c r="B212">
-        <v>-31.98247476190433</v>
+        <v>-31.982474761904331</v>
       </c>
       <c r="C212" t="s">
         <v>31</v>
@@ -2916,12 +2935,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>49</v>
       </c>
       <c r="B213">
-        <v>-0.006675900122927248</v>
+        <v>-6.6759001229272476E-3</v>
       </c>
       <c r="C213" t="s">
         <v>1</v>
@@ -2933,7 +2952,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>2</v>
       </c>
@@ -2941,7 +2960,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>4</v>
       </c>
@@ -2949,7 +2968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>5</v>
       </c>
@@ -2957,7 +2976,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>6</v>
       </c>
@@ -2965,7 +2984,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>7</v>
       </c>
@@ -2973,7 +2992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>8</v>
       </c>
@@ -2981,7 +3000,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>10</v>
       </c>
@@ -2989,12 +3008,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -3014,7 +3033,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>27</v>
       </c>
@@ -3031,7 +3050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>66</v>
       </c>
@@ -3048,7 +3067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>51</v>
       </c>
@@ -3065,12 +3084,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>39</v>
       </c>
       <c r="B227">
-        <v>0.3529411764705883</v>
+        <v>0.35294117647058831</v>
       </c>
       <c r="C227" t="s">
         <v>1</v>
@@ -3082,7 +3101,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>22</v>
       </c>
@@ -3099,7 +3118,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>2</v>
       </c>
@@ -3107,7 +3126,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>4</v>
       </c>
@@ -3115,7 +3134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>5</v>
       </c>
@@ -3123,7 +3142,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>6</v>
       </c>
@@ -3131,7 +3150,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>7</v>
       </c>
@@ -3139,7 +3158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:6">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>8</v>
       </c>
@@ -3147,7 +3166,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:6">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>10</v>
       </c>
@@ -3155,12 +3174,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="237" spans="1:6">
+    <row r="237" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="238" spans="1:6">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>13</v>
       </c>
@@ -3180,7 +3199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="239" spans="1:6">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>29</v>
       </c>
@@ -3197,7 +3216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:6">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>54</v>
       </c>
@@ -3214,7 +3233,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="241" spans="1:6">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>67</v>
       </c>
@@ -3231,7 +3250,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="243" spans="1:6">
+    <row r="243" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>2</v>
       </c>
@@ -3239,7 +3258,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="244" spans="1:6">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>4</v>
       </c>
@@ -3247,7 +3266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:6">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>5</v>
       </c>
@@ -3255,7 +3274,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="246" spans="1:6">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>6</v>
       </c>
@@ -3263,7 +3282,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="247" spans="1:6">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>7</v>
       </c>
@@ -3271,7 +3290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:6">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>8</v>
       </c>
@@ -3279,7 +3298,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:6">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>10</v>
       </c>
@@ -3287,12 +3306,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="250" spans="1:6">
+    <row r="250" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="251" spans="1:6">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>13</v>
       </c>
@@ -3312,7 +3331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="252" spans="1:6">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>52</v>
       </c>
@@ -3329,7 +3348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="253" spans="1:6">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>3</v>
       </c>
@@ -3346,12 +3365,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="254" spans="1:6">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>48</v>
       </c>
       <c r="B254">
-        <v>0.4285714285714285</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="C254" t="s">
         <v>1</v>
@@ -3363,12 +3382,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="255" spans="1:6">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>39</v>
       </c>
       <c r="B255">
-        <v>0.2539135296797552</v>
+        <v>0.25391352967975522</v>
       </c>
       <c r="C255" t="s">
         <v>1</v>
@@ -3380,7 +3399,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="257" spans="1:6">
+    <row r="257" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>2</v>
       </c>
@@ -3388,7 +3407,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="258" spans="1:6">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>4</v>
       </c>
@@ -3396,7 +3415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:6">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>5</v>
       </c>
@@ -3404,7 +3423,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="260" spans="1:6">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>6</v>
       </c>
@@ -3412,7 +3431,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="261" spans="1:6">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>7</v>
       </c>
@@ -3420,7 +3439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:6">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>8</v>
       </c>
@@ -3428,7 +3447,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="263" spans="1:6">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>10</v>
       </c>
@@ -3436,12 +3455,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="264" spans="1:6">
+    <row r="264" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="265" spans="1:6">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>13</v>
       </c>
@@ -3461,7 +3480,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="266" spans="1:6">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>53</v>
       </c>
@@ -3478,7 +3497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:6">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>3</v>
       </c>
@@ -3495,12 +3514,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:6">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>50</v>
       </c>
       <c r="B268">
-        <v>0.4285714285714285</v>
+        <v>0.42857142857142849</v>
       </c>
       <c r="C268" t="s">
         <v>1</v>
@@ -3512,12 +3531,12 @@
         <v>25</v>
       </c>
     </row>
-    <row r="269" spans="1:6">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>39</v>
       </c>
       <c r="B269">
-        <v>0.2539135296797552</v>
+        <v>0.25391352967975522</v>
       </c>
       <c r="C269" t="s">
         <v>1</v>
@@ -3529,7 +3548,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="1:6">
+    <row r="271" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>2</v>
       </c>
@@ -3537,7 +3556,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="272" spans="1:6">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>4</v>
       </c>
@@ -3545,7 +3564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:6">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>5</v>
       </c>
@@ -3553,7 +3572,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="274" spans="1:6">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>6</v>
       </c>
@@ -3561,7 +3580,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="275" spans="1:6">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>7</v>
       </c>
@@ -3569,7 +3588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:6">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>8</v>
       </c>
@@ -3577,7 +3596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:6">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>10</v>
       </c>
@@ -3585,12 +3604,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="278" spans="1:6">
+    <row r="278" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="279" spans="1:6">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>13</v>
       </c>
@@ -3610,7 +3629,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:6">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>15</v>
       </c>
@@ -3627,7 +3646,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:6">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>49</v>
       </c>
@@ -3644,7 +3663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:6">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>69</v>
       </c>
@@ -3664,4 +3683,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d465f887-04a9-4c17-8b62-103eddccf68b}" enabled="1" method="Standard" siteId="{ca2a7f76-dbd7-4ec0-9108-6b3d524fb7c8}" removed="0"/>
+</clbl:labelList>
 </file>